--- a/Data/DungeonEquipment.xlsx
+++ b/Data/DungeonEquipment.xlsx
@@ -8,27 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitFolder\ProjectTT\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{85369469-3DEE-4C2D-A991-FBC7FD7339A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684B9D9D-4B27-40DD-88B0-EB693E912716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6345" yWindow="4110" windowWidth="25350" windowHeight="10530" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DungeonEquipment" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="119">
   <si>
     <t>1000;1001;</t>
   </si>
   <si>
-    <t>3111;3121;3131;3141;3151;3161;</t>
-  </si>
-  <si>
     <t>Stage</t>
   </si>
   <si>
@@ -71,24 +67,6 @@
     <t>EffectRadius</t>
   </si>
   <si>
-    <t>RewardPointType1</t>
-  </si>
-  <si>
-    <t>RewardPointAmount1</t>
-  </si>
-  <si>
-    <t>RewardEquipmentItemIds</t>
-  </si>
-  <si>
-    <t>RewardEquipmentLevelMin</t>
-  </si>
-  <si>
-    <t>RewardEquipmentLevelMax</t>
-  </si>
-  <si>
-    <t>RewardEquipmentCount</t>
-  </si>
-  <si>
     <t>KillCountWithExplosion</t>
   </si>
   <si>
@@ -98,9 +76,6 @@
     <t>1000;</t>
   </si>
   <si>
-    <t>Gold</t>
-  </si>
-  <si>
     <t>Equip 2</t>
   </si>
   <si>
@@ -249,6 +224,160 @@
   </si>
   <si>
     <t>Equip 50</t>
+  </si>
+  <si>
+    <t>RewardPoints</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold=49</t>
+  </si>
+  <si>
+    <t>Gold=58</t>
+  </si>
+  <si>
+    <t>Gold=68</t>
+  </si>
+  <si>
+    <t>Gold=77</t>
+  </si>
+  <si>
+    <t>Gold=86</t>
+  </si>
+  <si>
+    <t>Gold=96</t>
+  </si>
+  <si>
+    <t>Gold=105</t>
+  </si>
+  <si>
+    <t>Gold=114</t>
+  </si>
+  <si>
+    <t>Gold=124</t>
+  </si>
+  <si>
+    <t>Gold=133</t>
+  </si>
+  <si>
+    <t>Gold=142</t>
+  </si>
+  <si>
+    <t>Gold=152</t>
+  </si>
+  <si>
+    <t>Gold=161</t>
+  </si>
+  <si>
+    <t>Gold=170</t>
+  </si>
+  <si>
+    <t>Gold=180</t>
+  </si>
+  <si>
+    <t>Gold=189</t>
+  </si>
+  <si>
+    <t>Gold=198</t>
+  </si>
+  <si>
+    <t>Gold=208</t>
+  </si>
+  <si>
+    <t>Gold=217</t>
+  </si>
+  <si>
+    <t>Gold=226</t>
+  </si>
+  <si>
+    <t>Gold=236</t>
+  </si>
+  <si>
+    <t>Gold=245</t>
+  </si>
+  <si>
+    <t>Gold=254</t>
+  </si>
+  <si>
+    <t>Gold=264</t>
+  </si>
+  <si>
+    <t>Gold=273</t>
+  </si>
+  <si>
+    <t>Gold=282</t>
+  </si>
+  <si>
+    <t>Gold=292</t>
+  </si>
+  <si>
+    <t>Gold=301</t>
+  </si>
+  <si>
+    <t>Gold=310</t>
+  </si>
+  <si>
+    <t>Gold=320</t>
+  </si>
+  <si>
+    <t>Gold=329</t>
+  </si>
+  <si>
+    <t>Gold=338</t>
+  </si>
+  <si>
+    <t>Gold=348</t>
+  </si>
+  <si>
+    <t>Gold=357</t>
+  </si>
+  <si>
+    <t>Gold=366</t>
+  </si>
+  <si>
+    <t>Gold=376</t>
+  </si>
+  <si>
+    <t>Gold=385</t>
+  </si>
+  <si>
+    <t>Gold=394</t>
+  </si>
+  <si>
+    <t>Gold=404</t>
+  </si>
+  <si>
+    <t>Gold=413</t>
+  </si>
+  <si>
+    <t>Gold=422</t>
+  </si>
+  <si>
+    <t>Gold=432</t>
+  </si>
+  <si>
+    <t>Gold=441</t>
+  </si>
+  <si>
+    <t>Gold=450</t>
+  </si>
+  <si>
+    <t>Gold=460</t>
+  </si>
+  <si>
+    <t>Gold=469</t>
+  </si>
+  <si>
+    <t>Gold=478</t>
+  </si>
+  <si>
+    <t>Gold=488</t>
+  </si>
+  <si>
+    <t>Gold=497</t>
+  </si>
+  <si>
+    <t>Gold=506</t>
   </si>
 </sst>
 </file>
@@ -595,86 +724,71 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T51"/>
+  <dimension ref="A1:O51"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>8</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>12</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>13</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>14</v>
       </c>
-      <c r="N1" t="s">
-        <v>15</v>
-      </c>
       <c r="O1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
         <v>16</v>
-      </c>
-      <c r="P1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>18</v>
-      </c>
-      <c r="R1" t="s">
-        <v>19</v>
-      </c>
-      <c r="S1" t="s">
-        <v>20</v>
-      </c>
-      <c r="T1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
       </c>
       <c r="D2">
         <v>100001</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -704,39 +818,24 @@
         <v>2.42</v>
       </c>
       <c r="O2" t="s">
-        <v>25</v>
-      </c>
-      <c r="P2">
-        <v>49</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>5</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D3">
         <v>100002</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>13</v>
@@ -766,33 +865,18 @@
         <v>2.44</v>
       </c>
       <c r="O3" t="s">
-        <v>25</v>
-      </c>
-      <c r="P3">
-        <v>58</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>2</v>
-      </c>
-      <c r="S3">
-        <v>6</v>
-      </c>
-      <c r="T3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>100003</v>
@@ -828,39 +912,24 @@
         <v>2.46</v>
       </c>
       <c r="O4" t="s">
-        <v>25</v>
-      </c>
-      <c r="P4">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>3</v>
-      </c>
-      <c r="S4">
-        <v>7</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D5">
         <v>100004</v>
       </c>
       <c r="E5" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F5">
         <v>14</v>
@@ -890,39 +959,24 @@
         <v>2.48</v>
       </c>
       <c r="O5" t="s">
-        <v>25</v>
-      </c>
-      <c r="P5">
-        <v>77</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>4</v>
-      </c>
-      <c r="S5">
-        <v>8</v>
-      </c>
-      <c r="T5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
       </c>
       <c r="D6">
         <v>100005</v>
       </c>
       <c r="E6" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F6">
         <v>14</v>
@@ -952,33 +1006,18 @@
         <v>2.5</v>
       </c>
       <c r="O6" t="s">
-        <v>25</v>
-      </c>
-      <c r="P6">
-        <v>86</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>5</v>
-      </c>
-      <c r="S6">
-        <v>9</v>
-      </c>
-      <c r="T6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D7">
         <v>100006</v>
@@ -1014,39 +1053,24 @@
         <v>2.52</v>
       </c>
       <c r="O7" t="s">
-        <v>25</v>
-      </c>
-      <c r="P7">
-        <v>96</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>6</v>
-      </c>
-      <c r="S7">
-        <v>10</v>
-      </c>
-      <c r="T7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D8">
         <v>100007</v>
       </c>
       <c r="E8" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F8">
         <v>15</v>
@@ -1076,39 +1100,24 @@
         <v>2.54</v>
       </c>
       <c r="O8" t="s">
-        <v>25</v>
-      </c>
-      <c r="P8">
-        <v>105</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>7</v>
-      </c>
-      <c r="S8">
-        <v>11</v>
-      </c>
-      <c r="T8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D9">
         <v>100008</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F9">
         <v>16</v>
@@ -1138,33 +1147,18 @@
         <v>2.56</v>
       </c>
       <c r="O9" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9">
-        <v>114</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9">
-        <v>8</v>
-      </c>
-      <c r="S9">
-        <v>12</v>
-      </c>
-      <c r="T9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D10">
         <v>100009</v>
@@ -1200,39 +1194,24 @@
         <v>2.58</v>
       </c>
       <c r="O10" t="s">
-        <v>25</v>
-      </c>
-      <c r="P10">
-        <v>124</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10">
-        <v>9</v>
-      </c>
-      <c r="S10">
-        <v>13</v>
-      </c>
-      <c r="T10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D11">
         <v>100010</v>
       </c>
       <c r="E11" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F11">
         <v>17</v>
@@ -1262,39 +1241,24 @@
         <v>2.6</v>
       </c>
       <c r="O11" t="s">
-        <v>25</v>
-      </c>
-      <c r="P11">
-        <v>133</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11">
-        <v>10</v>
-      </c>
-      <c r="S11">
-        <v>14</v>
-      </c>
-      <c r="T11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>100011</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F12">
         <v>17</v>
@@ -1324,33 +1288,18 @@
         <v>2.62</v>
       </c>
       <c r="O12" t="s">
-        <v>25</v>
-      </c>
-      <c r="P12">
-        <v>142</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12">
-        <v>11</v>
-      </c>
-      <c r="S12">
-        <v>15</v>
-      </c>
-      <c r="T12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C13" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D13">
         <v>100012</v>
@@ -1386,39 +1335,24 @@
         <v>2.64</v>
       </c>
       <c r="O13" t="s">
-        <v>25</v>
-      </c>
-      <c r="P13">
-        <v>152</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13">
-        <v>12</v>
-      </c>
-      <c r="S13">
-        <v>16</v>
-      </c>
-      <c r="T13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C14" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D14">
         <v>100013</v>
       </c>
       <c r="E14" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F14">
         <v>18</v>
@@ -1448,39 +1382,24 @@
         <v>2.66</v>
       </c>
       <c r="O14" t="s">
-        <v>25</v>
-      </c>
-      <c r="P14">
-        <v>161</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14">
-        <v>13</v>
-      </c>
-      <c r="S14">
-        <v>17</v>
-      </c>
-      <c r="T14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>100014</v>
       </c>
       <c r="E15" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F15">
         <v>19</v>
@@ -1510,33 +1429,18 @@
         <v>2.68</v>
       </c>
       <c r="O15" t="s">
-        <v>25</v>
-      </c>
-      <c r="P15">
-        <v>170</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15">
-        <v>14</v>
-      </c>
-      <c r="S15">
-        <v>18</v>
-      </c>
-      <c r="T15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D16">
         <v>100015</v>
@@ -1572,39 +1476,24 @@
         <v>2.7</v>
       </c>
       <c r="O16" t="s">
-        <v>25</v>
-      </c>
-      <c r="P16">
-        <v>180</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>1</v>
-      </c>
-      <c r="R16">
-        <v>15</v>
-      </c>
-      <c r="S16">
-        <v>19</v>
-      </c>
-      <c r="T16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D17">
         <v>100016</v>
       </c>
       <c r="E17" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F17">
         <v>20</v>
@@ -1634,39 +1523,24 @@
         <v>2.72</v>
       </c>
       <c r="O17" t="s">
-        <v>25</v>
-      </c>
-      <c r="P17">
-        <v>189</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>1</v>
-      </c>
-      <c r="R17">
-        <v>16</v>
-      </c>
-      <c r="S17">
-        <v>20</v>
-      </c>
-      <c r="T17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C18" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D18">
         <v>100017</v>
       </c>
       <c r="E18" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F18">
         <v>20</v>
@@ -1696,33 +1570,18 @@
         <v>2.74</v>
       </c>
       <c r="O18" t="s">
-        <v>25</v>
-      </c>
-      <c r="P18">
-        <v>198</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>1</v>
-      </c>
-      <c r="R18">
-        <v>17</v>
-      </c>
-      <c r="S18">
-        <v>21</v>
-      </c>
-      <c r="T18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C19" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D19">
         <v>100018</v>
@@ -1758,39 +1617,24 @@
         <v>2.76</v>
       </c>
       <c r="O19" t="s">
-        <v>25</v>
-      </c>
-      <c r="P19">
-        <v>208</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>1</v>
-      </c>
-      <c r="R19">
-        <v>18</v>
-      </c>
-      <c r="S19">
-        <v>22</v>
-      </c>
-      <c r="T19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C20" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D20">
         <v>100019</v>
       </c>
       <c r="E20" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F20">
         <v>21</v>
@@ -1820,39 +1664,24 @@
         <v>2.78</v>
       </c>
       <c r="O20" t="s">
-        <v>25</v>
-      </c>
-      <c r="P20">
-        <v>217</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>1</v>
-      </c>
-      <c r="R20">
-        <v>19</v>
-      </c>
-      <c r="S20">
-        <v>23</v>
-      </c>
-      <c r="T20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>100020</v>
       </c>
       <c r="E21" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F21">
         <v>22</v>
@@ -1882,33 +1711,18 @@
         <v>2.8</v>
       </c>
       <c r="O21" t="s">
-        <v>25</v>
-      </c>
-      <c r="P21">
-        <v>226</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>1</v>
-      </c>
-      <c r="R21">
-        <v>20</v>
-      </c>
-      <c r="S21">
-        <v>24</v>
-      </c>
-      <c r="T21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C22" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D22">
         <v>100021</v>
@@ -1944,39 +1758,24 @@
         <v>2.82</v>
       </c>
       <c r="O22" t="s">
-        <v>25</v>
-      </c>
-      <c r="P22">
-        <v>236</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>1</v>
-      </c>
-      <c r="R22">
-        <v>21</v>
-      </c>
-      <c r="S22">
-        <v>25</v>
-      </c>
-      <c r="T22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D23">
         <v>100022</v>
       </c>
       <c r="E23" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F23">
         <v>23</v>
@@ -2006,39 +1805,24 @@
         <v>2.84</v>
       </c>
       <c r="O23" t="s">
-        <v>25</v>
-      </c>
-      <c r="P23">
-        <v>245</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>1</v>
-      </c>
-      <c r="R23">
-        <v>22</v>
-      </c>
-      <c r="S23">
-        <v>26</v>
-      </c>
-      <c r="T23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D24">
         <v>100023</v>
       </c>
       <c r="E24" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F24">
         <v>23</v>
@@ -2068,33 +1852,18 @@
         <v>2.86</v>
       </c>
       <c r="O24" t="s">
-        <v>25</v>
-      </c>
-      <c r="P24">
-        <v>254</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>1</v>
-      </c>
-      <c r="R24">
-        <v>23</v>
-      </c>
-      <c r="S24">
-        <v>27</v>
-      </c>
-      <c r="T24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D25">
         <v>100024</v>
@@ -2130,39 +1899,24 @@
         <v>2.88</v>
       </c>
       <c r="O25" t="s">
-        <v>25</v>
-      </c>
-      <c r="P25">
-        <v>264</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>1</v>
-      </c>
-      <c r="R25">
-        <v>24</v>
-      </c>
-      <c r="S25">
-        <v>28</v>
-      </c>
-      <c r="T25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C26" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D26">
         <v>100025</v>
       </c>
       <c r="E26" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F26">
         <v>24</v>
@@ -2192,39 +1946,24 @@
         <v>2.9</v>
       </c>
       <c r="O26" t="s">
-        <v>25</v>
-      </c>
-      <c r="P26">
-        <v>273</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>1</v>
-      </c>
-      <c r="R26">
-        <v>25</v>
-      </c>
-      <c r="S26">
-        <v>29</v>
-      </c>
-      <c r="T26">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D27">
         <v>100026</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F27">
         <v>25</v>
@@ -2254,33 +1993,18 @@
         <v>2.92</v>
       </c>
       <c r="O27" t="s">
-        <v>25</v>
-      </c>
-      <c r="P27">
-        <v>282</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>1</v>
-      </c>
-      <c r="R27">
-        <v>26</v>
-      </c>
-      <c r="S27">
-        <v>30</v>
-      </c>
-      <c r="T27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D28">
         <v>100027</v>
@@ -2316,39 +2040,24 @@
         <v>2.94</v>
       </c>
       <c r="O28" t="s">
-        <v>25</v>
-      </c>
-      <c r="P28">
-        <v>292</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>1</v>
-      </c>
-      <c r="R28">
-        <v>27</v>
-      </c>
-      <c r="S28">
-        <v>31</v>
-      </c>
-      <c r="T28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C29" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D29">
         <v>100028</v>
       </c>
       <c r="E29" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F29">
         <v>26</v>
@@ -2378,39 +2087,24 @@
         <v>2.96</v>
       </c>
       <c r="O29" t="s">
-        <v>25</v>
-      </c>
-      <c r="P29">
-        <v>301</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>1</v>
-      </c>
-      <c r="R29">
-        <v>28</v>
-      </c>
-      <c r="S29">
-        <v>32</v>
-      </c>
-      <c r="T29">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C30" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="D30">
         <v>100029</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F30">
         <v>26</v>
@@ -2440,33 +2134,18 @@
         <v>2.98</v>
       </c>
       <c r="O30" t="s">
-        <v>25</v>
-      </c>
-      <c r="P30">
-        <v>310</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>1</v>
-      </c>
-      <c r="R30">
-        <v>29</v>
-      </c>
-      <c r="S30">
-        <v>33</v>
-      </c>
-      <c r="T30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C31" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="D31">
         <v>100030</v>
@@ -2502,39 +2181,24 @@
         <v>3</v>
       </c>
       <c r="O31" t="s">
-        <v>25</v>
-      </c>
-      <c r="P31">
-        <v>320</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>1</v>
-      </c>
-      <c r="R31">
-        <v>30</v>
-      </c>
-      <c r="S31">
-        <v>34</v>
-      </c>
-      <c r="T31">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C32" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D32">
         <v>100031</v>
       </c>
       <c r="E32" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F32">
         <v>27</v>
@@ -2564,39 +2228,24 @@
         <v>3.02</v>
       </c>
       <c r="O32" t="s">
-        <v>25</v>
-      </c>
-      <c r="P32">
-        <v>329</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>1</v>
-      </c>
-      <c r="R32">
-        <v>31</v>
-      </c>
-      <c r="S32">
-        <v>35</v>
-      </c>
-      <c r="T32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="D33">
         <v>100032</v>
       </c>
       <c r="E33" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F33">
         <v>28</v>
@@ -2626,33 +2275,18 @@
         <v>3.04</v>
       </c>
       <c r="O33" t="s">
-        <v>25</v>
-      </c>
-      <c r="P33">
-        <v>338</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>1</v>
-      </c>
-      <c r="R33">
-        <v>32</v>
-      </c>
-      <c r="S33">
-        <v>36</v>
-      </c>
-      <c r="T33">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="D34">
         <v>100033</v>
@@ -2688,39 +2322,24 @@
         <v>3.06</v>
       </c>
       <c r="O34" t="s">
-        <v>25</v>
-      </c>
-      <c r="P34">
-        <v>348</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>1</v>
-      </c>
-      <c r="R34">
-        <v>33</v>
-      </c>
-      <c r="S34">
-        <v>37</v>
-      </c>
-      <c r="T34">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C35" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D35">
         <v>100034</v>
       </c>
       <c r="E35" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F35">
         <v>28</v>
@@ -2750,39 +2369,24 @@
         <v>3.08</v>
       </c>
       <c r="O35" t="s">
-        <v>25</v>
-      </c>
-      <c r="P35">
-        <v>357</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>1</v>
-      </c>
-      <c r="R35">
-        <v>34</v>
-      </c>
-      <c r="S35">
-        <v>38</v>
-      </c>
-      <c r="T35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="D36">
         <v>100035</v>
       </c>
       <c r="E36" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F36">
         <v>28</v>
@@ -2812,33 +2416,18 @@
         <v>3.1</v>
       </c>
       <c r="O36" t="s">
-        <v>25</v>
-      </c>
-      <c r="P36">
-        <v>366</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>1</v>
-      </c>
-      <c r="R36">
-        <v>35</v>
-      </c>
-      <c r="S36">
-        <v>39</v>
-      </c>
-      <c r="T36">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C37" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D37">
         <v>100036</v>
@@ -2874,39 +2463,24 @@
         <v>3.12</v>
       </c>
       <c r="O37" t="s">
-        <v>25</v>
-      </c>
-      <c r="P37">
-        <v>376</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>1</v>
-      </c>
-      <c r="R37">
-        <v>36</v>
-      </c>
-      <c r="S37">
-        <v>40</v>
-      </c>
-      <c r="T37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C38" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D38">
         <v>100037</v>
       </c>
       <c r="E38" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F38">
         <v>28</v>
@@ -2936,39 +2510,24 @@
         <v>3.14</v>
       </c>
       <c r="O38" t="s">
-        <v>25</v>
-      </c>
-      <c r="P38">
-        <v>385</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>1</v>
-      </c>
-      <c r="R38">
-        <v>37</v>
-      </c>
-      <c r="S38">
-        <v>41</v>
-      </c>
-      <c r="T38">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C39" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D39">
         <v>100038</v>
       </c>
       <c r="E39" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F39">
         <v>28</v>
@@ -2998,33 +2557,18 @@
         <v>3.16</v>
       </c>
       <c r="O39" t="s">
-        <v>25</v>
-      </c>
-      <c r="P39">
-        <v>394</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>1</v>
-      </c>
-      <c r="R39">
-        <v>38</v>
-      </c>
-      <c r="S39">
-        <v>42</v>
-      </c>
-      <c r="T39">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C40" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D40">
         <v>100039</v>
@@ -3060,39 +2604,24 @@
         <v>3.18</v>
       </c>
       <c r="O40" t="s">
-        <v>25</v>
-      </c>
-      <c r="P40">
-        <v>404</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>1</v>
-      </c>
-      <c r="R40">
-        <v>39</v>
-      </c>
-      <c r="S40">
-        <v>43</v>
-      </c>
-      <c r="T40">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C41" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>100040</v>
       </c>
       <c r="E41" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F41">
         <v>28</v>
@@ -3122,39 +2651,24 @@
         <v>3.2</v>
       </c>
       <c r="O41" t="s">
-        <v>25</v>
-      </c>
-      <c r="P41">
-        <v>413</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>1</v>
-      </c>
-      <c r="R41">
-        <v>40</v>
-      </c>
-      <c r="S41">
-        <v>44</v>
-      </c>
-      <c r="T41">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C42" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D42">
         <v>100041</v>
       </c>
       <c r="E42" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F42">
         <v>28</v>
@@ -3184,33 +2698,18 @@
         <v>3.22</v>
       </c>
       <c r="O42" t="s">
-        <v>25</v>
-      </c>
-      <c r="P42">
-        <v>422</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>1</v>
-      </c>
-      <c r="R42">
-        <v>41</v>
-      </c>
-      <c r="S42">
-        <v>45</v>
-      </c>
-      <c r="T42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C43" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="D43">
         <v>100042</v>
@@ -3246,39 +2745,24 @@
         <v>3.24</v>
       </c>
       <c r="O43" t="s">
-        <v>25</v>
-      </c>
-      <c r="P43">
-        <v>432</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>1</v>
-      </c>
-      <c r="R43">
-        <v>42</v>
-      </c>
-      <c r="S43">
-        <v>46</v>
-      </c>
-      <c r="T43">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C44" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="D44">
         <v>100043</v>
       </c>
       <c r="E44" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F44">
         <v>28</v>
@@ -3308,39 +2792,24 @@
         <v>3.26</v>
       </c>
       <c r="O44" t="s">
-        <v>25</v>
-      </c>
-      <c r="P44">
-        <v>441</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>43</v>
-      </c>
-      <c r="S44">
-        <v>47</v>
-      </c>
-      <c r="T44">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" x14ac:dyDescent="0.3">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C45" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D45">
         <v>100044</v>
       </c>
       <c r="E45" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F45">
         <v>28</v>
@@ -3370,33 +2839,18 @@
         <v>3.28</v>
       </c>
       <c r="O45" t="s">
-        <v>25</v>
-      </c>
-      <c r="P45">
-        <v>450</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>1</v>
-      </c>
-      <c r="R45">
-        <v>44</v>
-      </c>
-      <c r="S45">
-        <v>48</v>
-      </c>
-      <c r="T45">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D46">
         <v>100045</v>
@@ -3432,39 +2886,24 @@
         <v>3.3</v>
       </c>
       <c r="O46" t="s">
-        <v>25</v>
-      </c>
-      <c r="P46">
-        <v>460</v>
-      </c>
-      <c r="Q46" t="s">
-        <v>1</v>
-      </c>
-      <c r="R46">
-        <v>45</v>
-      </c>
-      <c r="S46">
-        <v>49</v>
-      </c>
-      <c r="T46">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C47" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="D47">
         <v>100046</v>
       </c>
       <c r="E47" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F47">
         <v>28</v>
@@ -3494,39 +2933,24 @@
         <v>3.32</v>
       </c>
       <c r="O47" t="s">
-        <v>25</v>
-      </c>
-      <c r="P47">
-        <v>469</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>1</v>
-      </c>
-      <c r="R47">
-        <v>46</v>
-      </c>
-      <c r="S47">
-        <v>50</v>
-      </c>
-      <c r="T47">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D48">
         <v>100047</v>
       </c>
       <c r="E48" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F48">
         <v>28</v>
@@ -3556,33 +2980,18 @@
         <v>3.34</v>
       </c>
       <c r="O48" t="s">
-        <v>25</v>
-      </c>
-      <c r="P48">
-        <v>478</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>1</v>
-      </c>
-      <c r="R48">
-        <v>47</v>
-      </c>
-      <c r="S48">
-        <v>51</v>
-      </c>
-      <c r="T48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C49" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D49">
         <v>100048</v>
@@ -3618,39 +3027,24 @@
         <v>3.36</v>
       </c>
       <c r="O49" t="s">
-        <v>25</v>
-      </c>
-      <c r="P49">
-        <v>488</v>
-      </c>
-      <c r="Q49" t="s">
-        <v>1</v>
-      </c>
-      <c r="R49">
-        <v>48</v>
-      </c>
-      <c r="S49">
-        <v>52</v>
-      </c>
-      <c r="T49">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C50" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D50">
         <v>100049</v>
       </c>
       <c r="E50" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F50">
         <v>28</v>
@@ -3680,39 +3074,24 @@
         <v>3.38</v>
       </c>
       <c r="O50" t="s">
-        <v>25</v>
-      </c>
-      <c r="P50">
-        <v>497</v>
-      </c>
-      <c r="Q50" t="s">
-        <v>1</v>
-      </c>
-      <c r="R50">
-        <v>49</v>
-      </c>
-      <c r="S50">
-        <v>53</v>
-      </c>
-      <c r="T50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C51" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D51">
         <v>100050</v>
       </c>
       <c r="E51" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="F51">
         <v>28</v>
@@ -3742,22 +3121,7 @@
         <v>3.4</v>
       </c>
       <c r="O51" t="s">
-        <v>25</v>
-      </c>
-      <c r="P51">
-        <v>506</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>1</v>
-      </c>
-      <c r="R51">
-        <v>50</v>
-      </c>
-      <c r="S51">
-        <v>54</v>
-      </c>
-      <c r="T51">
-        <v>2</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
